--- a/outputs/excel/benchmark_summary.xlsx
+++ b/outputs/excel/benchmark_summary.xlsx
@@ -493,28 +493,28 @@
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>30.99</v>
+        <v>32.1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.27</v>
+        <v>0.85</v>
       </c>
       <c r="F2" t="n">
-        <v>30.78</v>
+        <v>31.37</v>
       </c>
       <c r="G2" t="n">
-        <v>31.29</v>
+        <v>33.03</v>
       </c>
       <c r="H2" t="n">
-        <v>30.24</v>
+        <v>30.68</v>
       </c>
       <c r="I2" t="n">
-        <v>42.05</v>
+        <v>44.12</v>
       </c>
       <c r="J2" t="n">
-        <v>320.85</v>
+        <v>309.91</v>
       </c>
       <c r="K2" t="n">
-        <v>320.85</v>
+        <v>309.91</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -535,28 +535,28 @@
         <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>146.8</v>
+        <v>155.37</v>
       </c>
       <c r="E3" t="n">
-        <v>1.19</v>
+        <v>7.03</v>
       </c>
       <c r="F3" t="n">
-        <v>145.64</v>
+        <v>148.72</v>
       </c>
       <c r="G3" t="n">
-        <v>148.02</v>
+        <v>162.72</v>
       </c>
       <c r="H3" t="n">
-        <v>139.68</v>
+        <v>145.55</v>
       </c>
       <c r="I3" t="n">
-        <v>184.31</v>
+        <v>200.99</v>
       </c>
       <c r="J3" t="n">
-        <v>340.25</v>
+        <v>321.91</v>
       </c>
       <c r="K3" t="n">
-        <v>340.25</v>
+        <v>321.91</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -577,28 +577,28 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>289.25</v>
+        <v>306.83</v>
       </c>
       <c r="E4" t="n">
-        <v>2.25</v>
+        <v>14.17</v>
       </c>
       <c r="F4" t="n">
-        <v>287.86</v>
+        <v>296.63</v>
       </c>
       <c r="G4" t="n">
-        <v>291.85</v>
+        <v>323</v>
       </c>
       <c r="H4" t="n">
-        <v>279.81</v>
+        <v>292.42</v>
       </c>
       <c r="I4" t="n">
-        <v>362.91</v>
+        <v>390.75</v>
       </c>
       <c r="J4" t="n">
-        <v>345.49</v>
+        <v>326.14</v>
       </c>
       <c r="K4" t="n">
-        <v>345.49</v>
+        <v>326.14</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -619,31 +619,31 @@
         <v>200</v>
       </c>
       <c r="D5" t="n">
-        <v>571.62</v>
+        <v>615.08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.49</v>
+        <v>20.32</v>
       </c>
       <c r="F5" t="n">
-        <v>568.16</v>
+        <v>595.61</v>
       </c>
       <c r="G5" t="n">
-        <v>576.7</v>
+        <v>636.16</v>
       </c>
       <c r="H5" t="n">
-        <v>560.0599999999999</v>
+        <v>591.5700000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>640.22</v>
+        <v>780.92</v>
       </c>
       <c r="J5" t="n">
-        <v>349.68</v>
+        <v>325.18</v>
       </c>
       <c r="K5" t="n">
-        <v>349.68</v>
+        <v>325.18</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="6">
@@ -661,28 +661,28 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>28.24</v>
+        <v>29.62</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="F6" t="n">
-        <v>27.89</v>
+        <v>29.29</v>
       </c>
       <c r="G6" t="n">
-        <v>28.45</v>
+        <v>30.13</v>
       </c>
       <c r="H6" t="n">
-        <v>27.89</v>
+        <v>28.89</v>
       </c>
       <c r="I6" t="n">
-        <v>36.06</v>
+        <v>39.01</v>
       </c>
       <c r="J6" t="n">
-        <v>352.1</v>
+        <v>335.72</v>
       </c>
       <c r="K6" t="n">
-        <v>352.1</v>
+        <v>335.72</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -703,28 +703,28 @@
         <v>50</v>
       </c>
       <c r="D7" t="n">
-        <v>140.13</v>
+        <v>146.91</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="F7" t="n">
-        <v>139.75</v>
+        <v>146.29</v>
       </c>
       <c r="G7" t="n">
-        <v>140.77</v>
+        <v>147.92</v>
       </c>
       <c r="H7" t="n">
-        <v>128.81</v>
+        <v>133.29</v>
       </c>
       <c r="I7" t="n">
-        <v>198.79</v>
+        <v>211.42</v>
       </c>
       <c r="J7" t="n">
-        <v>356.4</v>
+        <v>339.96</v>
       </c>
       <c r="K7" t="n">
-        <v>356.4</v>
+        <v>339.96</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -745,28 +745,28 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>284.68</v>
+        <v>292.18</v>
       </c>
       <c r="E8" t="n">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="F8" t="n">
-        <v>283.21</v>
+        <v>291.22</v>
       </c>
       <c r="G8" t="n">
-        <v>286.24</v>
+        <v>293.48</v>
       </c>
       <c r="H8" t="n">
-        <v>271.16</v>
+        <v>275.99</v>
       </c>
       <c r="I8" t="n">
-        <v>404.92</v>
+        <v>417</v>
       </c>
       <c r="J8" t="n">
-        <v>351.03</v>
+        <v>342.02</v>
       </c>
       <c r="K8" t="n">
-        <v>351.03</v>
+        <v>342.02</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -787,31 +787,31 @@
         <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>566.23</v>
+        <v>608.8099999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>4.47</v>
+        <v>17.77</v>
       </c>
       <c r="F9" t="n">
-        <v>561.41</v>
+        <v>597.59</v>
       </c>
       <c r="G9" t="n">
-        <v>570.25</v>
+        <v>629.3</v>
       </c>
       <c r="H9" t="n">
-        <v>550.3</v>
+        <v>579.75</v>
       </c>
       <c r="I9" t="n">
-        <v>765.36</v>
+        <v>838.63</v>
       </c>
       <c r="J9" t="n">
-        <v>352.96</v>
+        <v>328.43</v>
       </c>
       <c r="K9" t="n">
-        <v>352.96</v>
+        <v>328.43</v>
       </c>
       <c r="L9" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="10">
@@ -829,28 +829,28 @@
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>166.28</v>
+        <v>172.54</v>
       </c>
       <c r="E10" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="F10" t="n">
-        <v>165.91</v>
+        <v>172.13</v>
       </c>
       <c r="G10" t="n">
-        <v>166.59</v>
+        <v>172.88</v>
       </c>
       <c r="H10" t="n">
-        <v>166.26</v>
+        <v>172.66</v>
       </c>
       <c r="I10" t="n">
-        <v>190.43</v>
+        <v>197.28</v>
       </c>
       <c r="J10" t="n">
-        <v>60.05</v>
+        <v>57.88</v>
       </c>
       <c r="K10" t="n">
-        <v>60.05</v>
+        <v>57.88</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -871,28 +871,28 @@
         <v>50</v>
       </c>
       <c r="D11" t="n">
-        <v>831.2</v>
+        <v>876.16</v>
       </c>
       <c r="E11" t="n">
-        <v>3.53</v>
+        <v>4.37</v>
       </c>
       <c r="F11" t="n">
-        <v>828.3</v>
+        <v>871.1900000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>835.13</v>
+        <v>879.4299999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>831.73</v>
+        <v>877.79</v>
       </c>
       <c r="I11" t="n">
-        <v>859.54</v>
+        <v>915.3200000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>60.06</v>
+        <v>56.97</v>
       </c>
       <c r="K11" t="n">
-        <v>60.06</v>
+        <v>56.97</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -913,28 +913,28 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>1658.58</v>
+        <v>1737.51</v>
       </c>
       <c r="E12" t="n">
-        <v>3.15</v>
+        <v>18.82</v>
       </c>
       <c r="F12" t="n">
-        <v>1656.23</v>
+        <v>1716.78</v>
       </c>
       <c r="G12" t="n">
-        <v>1662.16</v>
+        <v>1753.49</v>
       </c>
       <c r="H12" t="n">
-        <v>1660.07</v>
+        <v>1747.34</v>
       </c>
       <c r="I12" t="n">
-        <v>1679.94</v>
+        <v>1790.45</v>
       </c>
       <c r="J12" t="n">
-        <v>60.12</v>
+        <v>57.39</v>
       </c>
       <c r="K12" t="n">
-        <v>60.12</v>
+        <v>57.39</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
@@ -955,28 +955,28 @@
         <v>200</v>
       </c>
       <c r="D13" t="n">
-        <v>3309.1</v>
+        <v>3494</v>
       </c>
       <c r="E13" t="n">
-        <v>7.48</v>
+        <v>4.36</v>
       </c>
       <c r="F13" t="n">
-        <v>3303.56</v>
+        <v>3491.42</v>
       </c>
       <c r="G13" t="n">
-        <v>3317.62</v>
+        <v>3499.04</v>
       </c>
       <c r="H13" t="n">
-        <v>3323.95</v>
+        <v>3518.49</v>
       </c>
       <c r="I13" t="n">
-        <v>3348.78</v>
+        <v>3583.26</v>
       </c>
       <c r="J13" t="n">
-        <v>60.11</v>
+        <v>56.91</v>
       </c>
       <c r="K13" t="n">
-        <v>60.11</v>
+        <v>56.91</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -997,28 +997,28 @@
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>16.16</v>
+        <v>17.6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="F14" t="n">
-        <v>15.82</v>
+        <v>17.35</v>
       </c>
       <c r="G14" t="n">
-        <v>16.36</v>
+        <v>17.99</v>
       </c>
       <c r="H14" t="n">
-        <v>15.68</v>
+        <v>17</v>
       </c>
       <c r="I14" t="n">
-        <v>21.72</v>
+        <v>24.6</v>
       </c>
       <c r="J14" t="n">
-        <v>613.12</v>
+        <v>563.3099999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>613.12</v>
+        <v>563.3099999999999</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1039,28 +1039,28 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>82.40000000000001</v>
+        <v>85.06</v>
       </c>
       <c r="E15" t="n">
-        <v>0.27</v>
+        <v>1.47</v>
       </c>
       <c r="F15" t="n">
-        <v>82.08</v>
+        <v>84.13</v>
       </c>
       <c r="G15" t="n">
-        <v>82.56999999999999</v>
+        <v>86.75</v>
       </c>
       <c r="H15" t="n">
-        <v>81.94</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>92.98</v>
+        <v>99.63</v>
       </c>
       <c r="J15" t="n">
-        <v>605.65</v>
+        <v>586.86</v>
       </c>
       <c r="K15" t="n">
-        <v>605.65</v>
+        <v>586.86</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1081,28 +1081,28 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>162.52</v>
+        <v>163.93</v>
       </c>
       <c r="E16" t="n">
-        <v>2.57</v>
+        <v>0.79</v>
       </c>
       <c r="F16" t="n">
-        <v>160.8</v>
+        <v>163.1</v>
       </c>
       <c r="G16" t="n">
-        <v>165.48</v>
+        <v>164.68</v>
       </c>
       <c r="H16" t="n">
-        <v>160.85</v>
+        <v>161.91</v>
       </c>
       <c r="I16" t="n">
-        <v>182.67</v>
+        <v>188.25</v>
       </c>
       <c r="J16" t="n">
-        <v>614.72</v>
+        <v>609.35</v>
       </c>
       <c r="K16" t="n">
-        <v>614.72</v>
+        <v>609.35</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1123,28 +1123,28 @@
         <v>200</v>
       </c>
       <c r="D17" t="n">
-        <v>317.31</v>
+        <v>321.57</v>
       </c>
       <c r="E17" t="n">
-        <v>1.08</v>
+        <v>4.7</v>
       </c>
       <c r="F17" t="n">
-        <v>316.08</v>
+        <v>317.41</v>
       </c>
       <c r="G17" t="n">
-        <v>318.1</v>
+        <v>326.67</v>
       </c>
       <c r="H17" t="n">
-        <v>315.7</v>
+        <v>318.61</v>
       </c>
       <c r="I17" t="n">
-        <v>344.43</v>
+        <v>357.65</v>
       </c>
       <c r="J17" t="n">
-        <v>629.79</v>
+        <v>621.53</v>
       </c>
       <c r="K17" t="n">
-        <v>629.79</v>
+        <v>621.53</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1165,28 +1165,28 @@
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>21.91</v>
+        <v>22.94</v>
       </c>
       <c r="E18" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="F18" t="n">
-        <v>21.77</v>
+        <v>22.75</v>
       </c>
       <c r="G18" t="n">
-        <v>22.07</v>
+        <v>23.09</v>
       </c>
       <c r="H18" t="n">
-        <v>21.34</v>
+        <v>22.05</v>
       </c>
       <c r="I18" t="n">
-        <v>26.82</v>
+        <v>29.98</v>
       </c>
       <c r="J18" t="n">
-        <v>453.78</v>
+        <v>433.53</v>
       </c>
       <c r="K18" t="n">
-        <v>453.78</v>
+        <v>433.53</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1207,28 +1207,28 @@
         <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>109.18</v>
+        <v>113.9</v>
       </c>
       <c r="E19" t="n">
-        <v>1.26</v>
+        <v>2.12</v>
       </c>
       <c r="F19" t="n">
-        <v>107.94</v>
+        <v>112.29</v>
       </c>
       <c r="G19" t="n">
-        <v>110.45</v>
+        <v>116.31</v>
       </c>
       <c r="H19" t="n">
-        <v>107.88</v>
+        <v>112.49</v>
       </c>
       <c r="I19" t="n">
-        <v>118.75</v>
+        <v>126.84</v>
       </c>
       <c r="J19" t="n">
-        <v>457.5</v>
+        <v>438.6</v>
       </c>
       <c r="K19" t="n">
-        <v>457.5</v>
+        <v>438.6</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1249,28 +1249,28 @@
         <v>100</v>
       </c>
       <c r="D20" t="n">
-        <v>217.6</v>
+        <v>231.04</v>
       </c>
       <c r="E20" t="n">
-        <v>1.77</v>
+        <v>8.08</v>
       </c>
       <c r="F20" t="n">
-        <v>216.46</v>
+        <v>225.21</v>
       </c>
       <c r="G20" t="n">
-        <v>219.64</v>
+        <v>240.26</v>
       </c>
       <c r="H20" t="n">
-        <v>216.43</v>
+        <v>229.5</v>
       </c>
       <c r="I20" t="n">
-        <v>226.19</v>
+        <v>244.4</v>
       </c>
       <c r="J20" t="n">
-        <v>459.3</v>
+        <v>432.92</v>
       </c>
       <c r="K20" t="n">
-        <v>459.3</v>
+        <v>432.92</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1291,31 +1291,31 @@
         <v>200</v>
       </c>
       <c r="D21" t="n">
-        <v>437.07</v>
+        <v>465.43</v>
       </c>
       <c r="E21" t="n">
-        <v>1.04</v>
+        <v>18.3</v>
       </c>
       <c r="F21" t="n">
-        <v>435.91</v>
+        <v>453.82</v>
       </c>
       <c r="G21" t="n">
-        <v>437.93</v>
+        <v>486.52</v>
       </c>
       <c r="H21" t="n">
-        <v>433.47</v>
+        <v>463.2</v>
       </c>
       <c r="I21" t="n">
-        <v>453.43</v>
+        <v>482.05</v>
       </c>
       <c r="J21" t="n">
-        <v>457.39</v>
+        <v>429.92</v>
       </c>
       <c r="K21" t="n">
-        <v>457.39</v>
+        <v>429.92</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="22">
@@ -1333,28 +1333,28 @@
         <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>58.16</v>
+        <v>51</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="F22" t="n">
-        <v>58.02</v>
+        <v>50.65</v>
       </c>
       <c r="G22" t="n">
-        <v>58.39</v>
+        <v>51.29</v>
       </c>
       <c r="H22" t="n">
-        <v>56.75</v>
+        <v>49.9</v>
       </c>
       <c r="I22" t="n">
-        <v>76.23999999999999</v>
+        <v>65.33</v>
       </c>
       <c r="J22" t="n">
-        <v>171.25</v>
+        <v>195.24</v>
       </c>
       <c r="K22" t="n">
-        <v>171.25</v>
+        <v>195.24</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1375,28 +1375,28 @@
         <v>50</v>
       </c>
       <c r="D23" t="n">
-        <v>287.53</v>
+        <v>251.58</v>
       </c>
       <c r="E23" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="F23" t="n">
-        <v>285.72</v>
+        <v>249.17</v>
       </c>
       <c r="G23" t="n">
-        <v>289.01</v>
+        <v>253.76</v>
       </c>
       <c r="H23" t="n">
-        <v>284.62</v>
+        <v>248.38</v>
       </c>
       <c r="I23" t="n">
-        <v>334.39</v>
+        <v>287.44</v>
       </c>
       <c r="J23" t="n">
-        <v>173.69</v>
+        <v>198.52</v>
       </c>
       <c r="K23" t="n">
-        <v>173.69</v>
+        <v>198.52</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1417,31 +1417,31 @@
         <v>100</v>
       </c>
       <c r="D24" t="n">
-        <v>576.27</v>
+        <v>497.19</v>
       </c>
       <c r="E24" t="n">
-        <v>3.21</v>
+        <v>1.4</v>
       </c>
       <c r="F24" t="n">
-        <v>572.64</v>
+        <v>495.78</v>
       </c>
       <c r="G24" t="n">
-        <v>578.74</v>
+        <v>498.57</v>
       </c>
       <c r="H24" t="n">
-        <v>573.08</v>
+        <v>497.09</v>
       </c>
       <c r="I24" t="n">
-        <v>640.55</v>
+        <v>533.45</v>
       </c>
       <c r="J24" t="n">
-        <v>173.36</v>
+        <v>200.93</v>
       </c>
       <c r="K24" t="n">
-        <v>173.36</v>
+        <v>200.93</v>
       </c>
       <c r="L24" t="n">
-        <v>0.95</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="25">
@@ -1459,31 +1459,31 @@
         <v>200</v>
       </c>
       <c r="D25" t="n">
-        <v>1154.35</v>
+        <v>997.8</v>
       </c>
       <c r="E25" t="n">
-        <v>6.97</v>
+        <v>4.74</v>
       </c>
       <c r="F25" t="n">
-        <v>1146.42</v>
+        <v>993.58</v>
       </c>
       <c r="G25" t="n">
-        <v>1159.51</v>
+        <v>1002.94</v>
       </c>
       <c r="H25" t="n">
-        <v>1153.87</v>
+        <v>1000.22</v>
       </c>
       <c r="I25" t="n">
-        <v>1237.71</v>
+        <v>1049.18</v>
       </c>
       <c r="J25" t="n">
-        <v>173</v>
+        <v>200.17</v>
       </c>
       <c r="K25" t="n">
-        <v>173</v>
+        <v>200.17</v>
       </c>
       <c r="L25" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="26">
@@ -1501,28 +1501,28 @@
         <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>168.29</v>
+        <v>167.53</v>
       </c>
       <c r="E26" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="F26" t="n">
-        <v>168.2</v>
+        <v>167.41</v>
       </c>
       <c r="G26" t="n">
-        <v>168.45</v>
+        <v>167.62</v>
       </c>
       <c r="H26" t="n">
-        <v>168.19</v>
+        <v>167.46</v>
       </c>
       <c r="I26" t="n">
-        <v>193.25</v>
+        <v>192.38</v>
       </c>
       <c r="J26" t="n">
-        <v>59.34</v>
+        <v>59.61</v>
       </c>
       <c r="K26" t="n">
-        <v>59.34</v>
+        <v>59.61</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1543,28 +1543,28 @@
         <v>50</v>
       </c>
       <c r="D27" t="n">
-        <v>845.41</v>
+        <v>841.3099999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>3.63</v>
+        <v>6.74</v>
       </c>
       <c r="F27" t="n">
-        <v>842.86</v>
+        <v>834.0700000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>849.5700000000001</v>
+        <v>847.4</v>
       </c>
       <c r="H27" t="n">
-        <v>846.22</v>
+        <v>841.89</v>
       </c>
       <c r="I27" t="n">
-        <v>876.54</v>
+        <v>871.78</v>
       </c>
       <c r="J27" t="n">
-        <v>59.05</v>
+        <v>59.34</v>
       </c>
       <c r="K27" t="n">
-        <v>59.05</v>
+        <v>59.34</v>
       </c>
       <c r="L27" t="n">
         <v>1</v>
@@ -1585,28 +1585,28 @@
         <v>100</v>
       </c>
       <c r="D28" t="n">
-        <v>1687.15</v>
+        <v>1739.72</v>
       </c>
       <c r="E28" t="n">
-        <v>6.71</v>
+        <v>27.66</v>
       </c>
       <c r="F28" t="n">
-        <v>1683.09</v>
+        <v>1709.91</v>
       </c>
       <c r="G28" t="n">
-        <v>1694.9</v>
+        <v>1764.57</v>
       </c>
       <c r="H28" t="n">
-        <v>1690.06</v>
+        <v>1736.03</v>
       </c>
       <c r="I28" t="n">
-        <v>1727.91</v>
+        <v>1839.3</v>
       </c>
       <c r="J28" t="n">
-        <v>59.11</v>
+        <v>57.32</v>
       </c>
       <c r="K28" t="n">
-        <v>59.11</v>
+        <v>57.32</v>
       </c>
       <c r="L28" t="n">
         <v>1</v>
@@ -1627,28 +1627,28 @@
         <v>200</v>
       </c>
       <c r="D29" t="n">
-        <v>3359.53</v>
+        <v>3408.5</v>
       </c>
       <c r="E29" t="n">
-        <v>3.69</v>
+        <v>1.66</v>
       </c>
       <c r="F29" t="n">
-        <v>3355.91</v>
+        <v>3406.59</v>
       </c>
       <c r="G29" t="n">
-        <v>3363.29</v>
+        <v>3409.63</v>
       </c>
       <c r="H29" t="n">
-        <v>3377.68</v>
+        <v>3432.42</v>
       </c>
       <c r="I29" t="n">
-        <v>3433.74</v>
+        <v>3472.08</v>
       </c>
       <c r="J29" t="n">
-        <v>59.2</v>
+        <v>58.34</v>
       </c>
       <c r="K29" t="n">
-        <v>59.2</v>
+        <v>58.34</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -1669,28 +1669,28 @@
         <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>18.36</v>
+        <v>16.44</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="F30" t="n">
-        <v>18.23</v>
+        <v>16.4</v>
       </c>
       <c r="G30" t="n">
-        <v>18.59</v>
+        <v>16.48</v>
       </c>
       <c r="H30" t="n">
-        <v>17.71</v>
+        <v>15.89</v>
       </c>
       <c r="I30" t="n">
-        <v>24.17</v>
+        <v>21.19</v>
       </c>
       <c r="J30" t="n">
-        <v>541.0599999999999</v>
+        <v>604.24</v>
       </c>
       <c r="K30" t="n">
-        <v>541.0599999999999</v>
+        <v>604.24</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1711,28 +1711,28 @@
         <v>50</v>
       </c>
       <c r="D31" t="n">
-        <v>90.76000000000001</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>0.31</v>
+        <v>0.92</v>
       </c>
       <c r="F31" t="n">
-        <v>90.47</v>
+        <v>79.69</v>
       </c>
       <c r="G31" t="n">
-        <v>91.09999999999999</v>
+        <v>81.39</v>
       </c>
       <c r="H31" t="n">
-        <v>89.34</v>
+        <v>80.23</v>
       </c>
       <c r="I31" t="n">
-        <v>102.74</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>550.23</v>
+        <v>618.52</v>
       </c>
       <c r="K31" t="n">
-        <v>550.23</v>
+        <v>618.52</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1753,28 +1753,28 @@
         <v>100</v>
       </c>
       <c r="D32" t="n">
-        <v>180.82</v>
+        <v>157.18</v>
       </c>
       <c r="E32" t="n">
-        <v>5.44</v>
+        <v>0.7</v>
       </c>
       <c r="F32" t="n">
-        <v>177.58</v>
+        <v>156.41</v>
       </c>
       <c r="G32" t="n">
-        <v>187.1</v>
+        <v>157.77</v>
       </c>
       <c r="H32" t="n">
-        <v>177.95</v>
+        <v>155.71</v>
       </c>
       <c r="I32" t="n">
-        <v>204.25</v>
+        <v>171.29</v>
       </c>
       <c r="J32" t="n">
-        <v>552.97</v>
+        <v>635.73</v>
       </c>
       <c r="K32" t="n">
-        <v>552.97</v>
+        <v>635.73</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -1795,28 +1795,28 @@
         <v>200</v>
       </c>
       <c r="D33" t="n">
-        <v>358.69</v>
+        <v>309.64</v>
       </c>
       <c r="E33" t="n">
-        <v>13.3</v>
+        <v>1.71</v>
       </c>
       <c r="F33" t="n">
-        <v>349.97</v>
+        <v>307.67</v>
       </c>
       <c r="G33" t="n">
-        <v>374</v>
+        <v>310.73</v>
       </c>
       <c r="H33" t="n">
-        <v>354.95</v>
+        <v>308.03</v>
       </c>
       <c r="I33" t="n">
-        <v>397.3</v>
+        <v>329.57</v>
       </c>
       <c r="J33" t="n">
-        <v>557.73</v>
+        <v>645.53</v>
       </c>
       <c r="K33" t="n">
-        <v>557.73</v>
+        <v>645.53</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
